--- a/artfynd/A 7567-2021 artfynd.xlsx
+++ b/artfynd/A 7567-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 7567-2021 artfynd.xlsx
+++ b/artfynd/A 7567-2021 artfynd.xlsx
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122234845</v>
+        <v>122234756</v>
       </c>
       <c r="B6" t="n">
-        <v>90744</v>
+        <v>98175</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,41 +1140,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Alnön, Mpd</t>
+          <t>alnön, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>627190</v>
+        <v>627239</v>
       </c>
       <c r="R6" t="n">
-        <v>6918716</v>
+        <v>6918754</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1234,10 +1243,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122234756</v>
+        <v>122234805</v>
       </c>
       <c r="B7" t="n">
-        <v>98175</v>
+        <v>57390</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,50 +1255,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>alnön, Mpd</t>
+          <t>Alnön, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>627239</v>
+        <v>627199</v>
       </c>
       <c r="R7" t="n">
-        <v>6918754</v>
+        <v>6918739</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1324,13 +1333,17 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1349,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122234805</v>
+        <v>122234845</v>
       </c>
       <c r="B8" t="n">
-        <v>57390</v>
+        <v>90744</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1361,39 +1374,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1401,10 +1405,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>627199</v>
+        <v>627190</v>
       </c>
       <c r="R8" t="n">
-        <v>6918739</v>
+        <v>6918716</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1439,17 +1443,13 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7567-2021 artfynd.xlsx
+++ b/artfynd/A 7567-2021 artfynd.xlsx
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122234673</v>
+        <v>122234845</v>
       </c>
       <c r="B5" t="n">
-        <v>90779</v>
+        <v>90754</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,37 +1026,29 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1065,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>627228</v>
+        <v>627190</v>
       </c>
       <c r="R5" t="n">
-        <v>6918743</v>
+        <v>6918716</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1128,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122234756</v>
+        <v>122234673</v>
       </c>
       <c r="B6" t="n">
-        <v>98175</v>
+        <v>90789</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,50 +1132,49 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>alnön, Mpd</t>
+          <t>Alnön, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>627239</v>
+        <v>627228</v>
       </c>
       <c r="R6" t="n">
-        <v>6918754</v>
+        <v>6918743</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1362,10 +1353,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122234845</v>
+        <v>122234756</v>
       </c>
       <c r="B8" t="n">
-        <v>90744</v>
+        <v>98185</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,41 +1365,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Alnön, Mpd</t>
+          <t>alnön, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>627190</v>
+        <v>627239</v>
       </c>
       <c r="R8" t="n">
-        <v>6918716</v>
+        <v>6918754</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>

--- a/artfynd/A 7567-2021 artfynd.xlsx
+++ b/artfynd/A 7567-2021 artfynd.xlsx
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122234845</v>
+        <v>122234805</v>
       </c>
       <c r="B5" t="n">
-        <v>90754</v>
+        <v>57390</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,30 +1026,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1057,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>627190</v>
+        <v>627199</v>
       </c>
       <c r="R5" t="n">
-        <v>6918716</v>
+        <v>6918739</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1095,13 +1104,17 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1120,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122234673</v>
+        <v>122234756</v>
       </c>
       <c r="B6" t="n">
-        <v>90789</v>
+        <v>98185</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,49 +1145,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Alnön, Mpd</t>
+          <t>alnön, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>627228</v>
+        <v>627239</v>
       </c>
       <c r="R6" t="n">
-        <v>6918743</v>
+        <v>6918754</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1234,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122234805</v>
+        <v>122234673</v>
       </c>
       <c r="B7" t="n">
-        <v>57390</v>
+        <v>90789</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,21 +1264,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1272,13 +1286,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1286,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>627199</v>
+        <v>627228</v>
       </c>
       <c r="R7" t="n">
-        <v>6918739</v>
+        <v>6918743</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1324,17 +1337,13 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1353,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122234756</v>
+        <v>122234845</v>
       </c>
       <c r="B8" t="n">
-        <v>98185</v>
+        <v>90754</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1365,50 +1374,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>alnön, Mpd</t>
+          <t>Alnön, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>627239</v>
+        <v>627190</v>
       </c>
       <c r="R8" t="n">
-        <v>6918754</v>
+        <v>6918716</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>

--- a/artfynd/A 7567-2021 artfynd.xlsx
+++ b/artfynd/A 7567-2021 artfynd.xlsx
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122234805</v>
+        <v>122234673</v>
       </c>
       <c r="B5" t="n">
-        <v>57390</v>
+        <v>90801</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,21 +1030,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,13 +1052,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1066,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>627199</v>
+        <v>627228</v>
       </c>
       <c r="R5" t="n">
-        <v>6918739</v>
+        <v>6918743</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,17 +1103,13 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1133,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122234756</v>
+        <v>122234845</v>
       </c>
       <c r="B6" t="n">
-        <v>98185</v>
+        <v>90766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,50 +1140,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>alnön, Mpd</t>
+          <t>Alnön, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>627239</v>
+        <v>627190</v>
       </c>
       <c r="R6" t="n">
-        <v>6918754</v>
+        <v>6918716</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1248,10 +1234,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122234673</v>
+        <v>122234756</v>
       </c>
       <c r="B7" t="n">
-        <v>90789</v>
+        <v>98197</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,49 +1246,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Alnön, Mpd</t>
+          <t>alnön, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>627228</v>
+        <v>627239</v>
       </c>
       <c r="R7" t="n">
-        <v>6918743</v>
+        <v>6918754</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1362,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122234845</v>
+        <v>122234805</v>
       </c>
       <c r="B8" t="n">
-        <v>90754</v>
+        <v>57395</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,30 +1361,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1405,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>627190</v>
+        <v>627199</v>
       </c>
       <c r="R8" t="n">
-        <v>6918716</v>
+        <v>6918739</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1443,13 +1439,17 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7567-2021 artfynd.xlsx
+++ b/artfynd/A 7567-2021 artfynd.xlsx
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122234673</v>
+        <v>122234845</v>
       </c>
       <c r="B5" t="n">
-        <v>90801</v>
+        <v>90773</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,37 +1026,29 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1065,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>627228</v>
+        <v>627190</v>
       </c>
       <c r="R5" t="n">
-        <v>6918743</v>
+        <v>6918716</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1128,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122234845</v>
+        <v>122234805</v>
       </c>
       <c r="B6" t="n">
-        <v>90766</v>
+        <v>57395</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,30 +1132,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1171,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>627190</v>
+        <v>627199</v>
       </c>
       <c r="R6" t="n">
-        <v>6918716</v>
+        <v>6918739</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1209,13 +1210,17 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1234,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122234756</v>
+        <v>122234673</v>
       </c>
       <c r="B7" t="n">
-        <v>98197</v>
+        <v>90808</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,50 +1251,49 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>alnön, Mpd</t>
+          <t>Alnön, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>627239</v>
+        <v>627228</v>
       </c>
       <c r="R7" t="n">
-        <v>6918754</v>
+        <v>6918743</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1349,10 +1353,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122234805</v>
+        <v>122234756</v>
       </c>
       <c r="B8" t="n">
-        <v>57395</v>
+        <v>98202</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1361,50 +1365,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Alnön, Mpd</t>
+          <t>alnön, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>627199</v>
+        <v>627239</v>
       </c>
       <c r="R8" t="n">
-        <v>6918739</v>
+        <v>6918754</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1439,17 +1443,13 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7567-2021 artfynd.xlsx
+++ b/artfynd/A 7567-2021 artfynd.xlsx
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122234845</v>
+        <v>122234673</v>
       </c>
       <c r="B5" t="n">
-        <v>90773</v>
+        <v>90813</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,29 +1026,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>1202</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1057,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>627190</v>
+        <v>627228</v>
       </c>
       <c r="R5" t="n">
-        <v>6918716</v>
+        <v>6918743</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1120,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122234805</v>
+        <v>122234756</v>
       </c>
       <c r="B6" t="n">
-        <v>57395</v>
+        <v>98211</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,50 +1135,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Alnön, Mpd</t>
+          <t>alnön, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>627199</v>
+        <v>627239</v>
       </c>
       <c r="R6" t="n">
-        <v>6918739</v>
+        <v>6918754</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1210,17 +1208,13 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1239,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122234673</v>
+        <v>122234845</v>
       </c>
       <c r="B7" t="n">
-        <v>90808</v>
+        <v>90778</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,37 +1245,24 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>5447</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1290,10 +1271,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>627228</v>
+        <v>627190</v>
       </c>
       <c r="R7" t="n">
-        <v>6918743</v>
+        <v>6918716</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1353,10 +1334,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122234756</v>
+        <v>122234805</v>
       </c>
       <c r="B8" t="n">
-        <v>98202</v>
+        <v>57395</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1365,50 +1346,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>alnön, Mpd</t>
+          <t>Alnön, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>627239</v>
+        <v>627199</v>
       </c>
       <c r="R8" t="n">
-        <v>6918754</v>
+        <v>6918739</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1443,13 +1419,17 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7567-2021 artfynd.xlsx
+++ b/artfynd/A 7567-2021 artfynd.xlsx
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122234673</v>
+        <v>122234845</v>
       </c>
       <c r="B5" t="n">
-        <v>90813</v>
+        <v>90791</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,32 +1026,29 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5447</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1060,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>627228</v>
+        <v>627190</v>
       </c>
       <c r="R5" t="n">
-        <v>6918743</v>
+        <v>6918716</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1126,7 +1123,7 @@
         <v>122234756</v>
       </c>
       <c r="B6" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,6 +1137,11 @@
       </c>
       <c r="E6" t="n">
         <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1233,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122234845</v>
+        <v>122234805</v>
       </c>
       <c r="B7" t="n">
-        <v>90778</v>
+        <v>57399</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,25 +1247,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1271,10 +1287,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>627190</v>
+        <v>627199</v>
       </c>
       <c r="R7" t="n">
-        <v>6918716</v>
+        <v>6918739</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1309,13 +1325,17 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1334,10 +1354,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122234805</v>
+        <v>122234673</v>
       </c>
       <c r="B8" t="n">
-        <v>57395</v>
+        <v>90826</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1350,16 +1370,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1202</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1367,13 +1392,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1381,10 +1405,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>627199</v>
+        <v>627228</v>
       </c>
       <c r="R8" t="n">
-        <v>6918739</v>
+        <v>6918743</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1419,17 +1443,13 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7567-2021 artfynd.xlsx
+++ b/artfynd/A 7567-2021 artfynd.xlsx
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122234845</v>
+        <v>122234756</v>
       </c>
       <c r="B5" t="n">
-        <v>90791</v>
+        <v>98237</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,41 +1026,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Alnön, Mpd</t>
+          <t>alnön, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>627190</v>
+        <v>627239</v>
       </c>
       <c r="R5" t="n">
-        <v>6918716</v>
+        <v>6918754</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1120,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122234756</v>
+        <v>122234805</v>
       </c>
       <c r="B6" t="n">
-        <v>98224</v>
+        <v>57399</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,50 +1141,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>alnön, Mpd</t>
+          <t>Alnön, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>627239</v>
+        <v>627199</v>
       </c>
       <c r="R6" t="n">
-        <v>6918754</v>
+        <v>6918739</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1210,13 +1219,17 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1235,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122234805</v>
+        <v>122234845</v>
       </c>
       <c r="B7" t="n">
-        <v>57399</v>
+        <v>90804</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,39 +1260,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1287,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>627199</v>
+        <v>627190</v>
       </c>
       <c r="R7" t="n">
-        <v>6918739</v>
+        <v>6918716</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1325,17 +1329,13 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1357,7 +1357,7 @@
         <v>122234673</v>
       </c>
       <c r="B8" t="n">
-        <v>90826</v>
+        <v>90839</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 7567-2021 artfynd.xlsx
+++ b/artfynd/A 7567-2021 artfynd.xlsx
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122234756</v>
+        <v>122234673</v>
       </c>
       <c r="B5" t="n">
-        <v>98237</v>
+        <v>90839</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,50 +1026,49 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>alnön, Mpd</t>
+          <t>Alnön, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>627239</v>
+        <v>627228</v>
       </c>
       <c r="R5" t="n">
-        <v>6918754</v>
+        <v>6918743</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1129,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122234805</v>
+        <v>122234845</v>
       </c>
       <c r="B6" t="n">
-        <v>57399</v>
+        <v>90804</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,39 +1140,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1181,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>627199</v>
+        <v>627190</v>
       </c>
       <c r="R6" t="n">
-        <v>6918739</v>
+        <v>6918716</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1219,17 +1209,13 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1248,10 +1234,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122234845</v>
+        <v>122234756</v>
       </c>
       <c r="B7" t="n">
-        <v>90804</v>
+        <v>98237</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,41 +1246,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Alnön, Mpd</t>
+          <t>alnön, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>627190</v>
+        <v>627239</v>
       </c>
       <c r="R7" t="n">
-        <v>6918716</v>
+        <v>6918754</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1354,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122234673</v>
+        <v>122234805</v>
       </c>
       <c r="B8" t="n">
-        <v>90839</v>
+        <v>57399</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,21 +1365,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1392,12 +1387,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1405,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>627228</v>
+        <v>627199</v>
       </c>
       <c r="R8" t="n">
-        <v>6918743</v>
+        <v>6918739</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1443,13 +1439,17 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7567-2021 artfynd.xlsx
+++ b/artfynd/A 7567-2021 artfynd.xlsx
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122234673</v>
+        <v>122234805</v>
       </c>
       <c r="B5" t="n">
-        <v>90839</v>
+        <v>57399</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,21 +1030,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,12 +1052,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1065,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>627228</v>
+        <v>627199</v>
       </c>
       <c r="R5" t="n">
-        <v>6918743</v>
+        <v>6918739</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1103,13 +1104,17 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1128,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122234845</v>
+        <v>122234756</v>
       </c>
       <c r="B6" t="n">
-        <v>90804</v>
+        <v>98240</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,41 +1145,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Alnön, Mpd</t>
+          <t>alnön, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>627190</v>
+        <v>627239</v>
       </c>
       <c r="R6" t="n">
-        <v>6918716</v>
+        <v>6918754</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1234,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122234756</v>
+        <v>122234845</v>
       </c>
       <c r="B7" t="n">
-        <v>98237</v>
+        <v>90798</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,50 +1260,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>alnön, Mpd</t>
+          <t>Alnön, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>627239</v>
+        <v>627190</v>
       </c>
       <c r="R7" t="n">
-        <v>6918754</v>
+        <v>6918716</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1349,10 +1354,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122234805</v>
+        <v>122234673</v>
       </c>
       <c r="B8" t="n">
-        <v>57399</v>
+        <v>90833</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1365,21 +1370,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1387,13 +1392,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1401,10 +1405,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>627199</v>
+        <v>627228</v>
       </c>
       <c r="R8" t="n">
-        <v>6918739</v>
+        <v>6918743</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1439,17 +1443,13 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7567-2021 artfynd.xlsx
+++ b/artfynd/A 7567-2021 artfynd.xlsx
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122234805</v>
+        <v>122234673</v>
       </c>
       <c r="B5" t="n">
-        <v>57399</v>
+        <v>90833</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,21 +1030,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,13 +1052,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1066,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>627199</v>
+        <v>627228</v>
       </c>
       <c r="R5" t="n">
-        <v>6918739</v>
+        <v>6918743</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,17 +1103,13 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1133,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122234756</v>
+        <v>122234805</v>
       </c>
       <c r="B6" t="n">
-        <v>98240</v>
+        <v>57399</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,50 +1140,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>alnön, Mpd</t>
+          <t>Alnön, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>627239</v>
+        <v>627199</v>
       </c>
       <c r="R6" t="n">
-        <v>6918754</v>
+        <v>6918739</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1223,13 +1218,17 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1248,10 +1247,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122234845</v>
+        <v>122234756</v>
       </c>
       <c r="B7" t="n">
-        <v>90798</v>
+        <v>98240</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,41 +1259,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Alnön, Mpd</t>
+          <t>alnön, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>627190</v>
+        <v>627239</v>
       </c>
       <c r="R7" t="n">
-        <v>6918716</v>
+        <v>6918754</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1354,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122234673</v>
+        <v>122234845</v>
       </c>
       <c r="B8" t="n">
-        <v>90833</v>
+        <v>90798</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1366,37 +1374,29 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>627228</v>
+        <v>627190</v>
       </c>
       <c r="R8" t="n">
-        <v>6918743</v>
+        <v>6918716</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>

--- a/artfynd/A 7567-2021 artfynd.xlsx
+++ b/artfynd/A 7567-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1466,6 +1466,123 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128103888</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Trappberget, Alnö Sundsvall, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>627474</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6918753</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Hans Johansson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Hans Johansson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7567-2021 artfynd.xlsx
+++ b/artfynd/A 7567-2021 artfynd.xlsx
@@ -1471,7 +1471,7 @@
         <v>128103888</v>
       </c>
       <c r="B9" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 7567-2021 artfynd.xlsx
+++ b/artfynd/A 7567-2021 artfynd.xlsx
@@ -1471,7 +1471,7 @@
         <v>128103888</v>
       </c>
       <c r="B9" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 7567-2021 artfynd.xlsx
+++ b/artfynd/A 7567-2021 artfynd.xlsx
@@ -1471,7 +1471,7 @@
         <v>128103888</v>
       </c>
       <c r="B9" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
